--- a/results/job_matches_2026-08-31.xlsx
+++ b/results/job_matches_2026-08-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer II, Data (Cloud &amp; AI)</t>
+          <t>Senior Data Platform Engineer - Azure Databricks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed8a1f209612e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebb2e53d9fa7b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer</t>
+          <t>Engineer II, Data (Cloud &amp; AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab555e988dd3c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ed8a1f209612e2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Platform and Infrastructure Engineer</t>
+          <t>AIPowered Power BI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Solvonex</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32791637f5d1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=5865f55ab1e5c5e9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AIPowered Power BI Engineer</t>
+          <t>Senior Software Engineer/Software Engineer III (Data Engineering)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, GCP, Hive, Spark, Scala, Kafka, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5865f55ab1e5c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3dc3ae389abf7c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer/Software Engineer III (Data Engineering)</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hive, Spark, Scala, Kafka, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,322 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3dc3ae389abf7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Kearney, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae9405dc478084f</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc099d426154e9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6982f28b9756d95</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4728d485fd82b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Grand Island, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8a860e6f7c99c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab656d0ca3d815</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ALLO Communications</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b710a7f0b803f961</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Specialist - Data Engineering</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LTM Limited</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c9493a61af734ed1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>RBC</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73756c88cc20b24b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-31.xlsx
+++ b/results/job_matches_2026-08-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer II, Data (Cloud &amp; AI)</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ed8a1f209612e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c27d39498fc808</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AIPowered Power BI Engineer</t>
+          <t>Contract Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Trimont</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,87 +556,297 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5865f55ab1e5c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4eea8025f3ef7c6f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer/Software Engineer III (Data Engineering)</t>
+          <t>Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hive, Spark, Scala, Kafka, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3dc3ae389abf7c</t>
+          <t>https://www.indeed.com/viewjob?jk=65c0895f1de6239e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Infrastructure Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63a5617f761c6faa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AIPowered Power BI Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Torrance, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Snowflake Schema</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5865f55ab1e5c5e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fad893368beea94</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Azistinc.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Danforth, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4d86ffea72e55e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer/Software Engineer III (Data Engineering)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Hive, Spark, Scala, Kafka, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a3dc3ae389abf7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Specialist - Data Engineering</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>LTM Limited</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Tampa, FL, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D11" t="n">
         <v>10.4</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c9493a61af734ed1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2026 - Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad9985af3e772076</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-31.xlsx
+++ b/results/job_matches_2026-08-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer - Azure Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebb2e53d9fa7b</t>
+          <t>https://www.indeed.com/viewjob?jk=15bc705887f3d3f9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Senior Data Platform Engineer - Azure Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c27d39498fc808</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebb2e53d9fa7b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Contract Infrastructure Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Trimont</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eea8025f3ef7c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf686b10c85ee8a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>Cloud Vulnerability Management Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c0895f1de6239e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c68f432e3b3384</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>Technology Consultant - Cloud &amp; Full Stack Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Spark, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a5617f761c6faa</t>
+          <t>https://www.indeed.com/viewjob?jk=e9068d6b5e88e56b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AIPowered Power BI Engineer</t>
+          <t>Technology Consultant - Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5865f55ab1e5c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=aff7320f2676a7bb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,147 +706,1197 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fad893368beea94</t>
+          <t>https://www.indeed.com/viewjob?jk=a1afe8b7a5cf447e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Azure AI Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Azistinc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Danforth, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d86ffea72e55e7</t>
+          <t>https://www.indeed.com/viewjob?jk=58f19beac4a8df7f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer/Software Engineer III (Data Engineering)</t>
+          <t>BI / Data Architect (Remote)-4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hive, Spark, Scala, Kafka, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3dc3ae389abf7c</t>
+          <t>https://www.indeed.com/viewjob?jk=63e9cfe1d5416339</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9493a61af734ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c27d39498fc808</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Mid-Level Java Developer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Antra, Inc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37bd12e2b62f9cde</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>clickhouse</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aab1ba56e62f502</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer-4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe15a8ff19071aee</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Infrastructure Solutions Architect- Onsite- Richmond, VA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Infoorigin Inc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19db03ed84045bd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Infrastructure Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64e2dee8091e6c26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Infrastructure Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Skywalk Global</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65c0895f1de6239e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Infrastructure Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63a5617f761c6faa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fad893368beea94</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Azistinc.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Danforth, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4d86ffea72e55e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Federal Reserve Bank of Boston</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, ETL, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22baba519bae8200</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Energy Data Scientist</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Burlington, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea4dcf33b2c6a0fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Energy Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41548be738a76cc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Energy Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8103a63d2d3d1da7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Energy Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13f4312108b4db79</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Energy Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26603fc5c3af6f4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer/Software Engineer III (Data Engineering)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Hive, Spark, Scala, Kafka, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a3dc3ae389abf7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Decatur, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, Power BI, DataOps, MLOps</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9189c721d2bd01c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vantage Point Logistics</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Westerville, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a30d8a15dec2e27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Technology Development Program Associate - February 2027</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Development Infrastructure</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, Git</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fde89f0085f48d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cloud Destinations</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Athena, S3, Databricks, Spark, PySpark, Scala, ETL, ELT, Splunk</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0de81eafb3fefc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7088241af78eed3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Data Engineering Associate Consultant (Graduating Dec 2026 - Summer 2027)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>CapTech Consulting</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Richmond, VA, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D35" t="n">
         <v>10.4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ad9985af3e772076</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Enterprise Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Amway</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ada, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Cloud Storage, Scala, Kafka, CI/CD, Docker, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b546afd28257f1d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Shamrock Foods Company</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Commerce City, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fe730220968ca4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Shamrock Foods Company</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33309cfbf855421f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Oracle, SQL Server, PostgreSQL, ETL, Tableau, Tableau Server, Git</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=788a20ff7253f53b</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Xactus</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Broomall, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, ETL, MLflow, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dec641935aaf0ea6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>VIE - Software Engineer (based in Miami)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pelico</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d71007f33dca61fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ellipsis Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, Python, Scala, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39ec559199e3af57</t>
         </is>
       </c>
     </row>
